--- a/JsonConverter/ExcelFiles/TrainingPolicyData.xlsx
+++ b/JsonConverter/ExcelFiles/TrainingPolicyData.xlsx
@@ -21,139 +21,139 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
   <x:si>
+    <x:t>policy_standing_offense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피니쉬를 노리는 공격적인 주짓수 훈련 우선도를 높인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SortOrder</x:t>
+  </x:si>
+  <x:si>
+    <x:t>policy_rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cardio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Offense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Focus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Defense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴식 중심</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>policy_wrestling_defense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>policy_wrestling_offense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스탠딩 타격 공격 중심의 훈련 우선도를 높인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스탠딩 타격 방어 중심의 훈련 우선도를 높인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력과 카디오 시설의 훈련 우선도를 높인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>policy_cardio</x:t>
+  </x:si>
+  <x:si>
     <x:t>주짓수 방어 집중 훈련</x:t>
   </x:si>
   <x:si>
+    <x:t>AttractionBonus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>훈련 체력 회복을 우선한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스탠딩 타격 방어 집중 훈련</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격적인 주짓수 집중 훈련</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력과 카디오 집중 훈련</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레슬링 방어 집중 훈련</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스탠딩 타격 공격 집중 훈련</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격적 레슬링 집중 훈련</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recovery</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
+  <x:si>
     <x:t>레슬링 방어 중심 훈련 우선도를 높인다.</x:t>
   </x:si>
   <x:si>
     <x:t>공격적 레슬링 중심 훈련 우선도를 높인다.</x:t>
   </x:si>
   <x:si>
-    <x:t>policy_cardio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>policy_jj_offense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttractionBonus</x:t>
-  </x:si>
-  <x:si>
-    <x:t>훈련 체력 회복을 우선한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스탠딩 타격 방어 집중 훈련</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격적 레슬링 집중 훈련</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레슬링 방어 집중 훈련</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격적인 주짓수 집중 훈련</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SortOrder</x:t>
-  </x:si>
-  <x:si>
-    <x:t>policy_rest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>policy_wr_offense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피니쉬를 노리는 공격적인 주짓수 훈련 우선도를 높인다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>주짓수 방어 중심 훈련 우선도를 높인다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Cardio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Offense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HpStamina</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Focus</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스탠딩 타격 방어 중심의 훈련 우선도를 높인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스탠딩 타격 공격 중심의 훈련 우선도를 높인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체력과 카디오 시설의 훈련 우선도를 높인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Defense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recovery</x:t>
-  </x:si>
-  <x:si>
-    <x:t>policy_st_offense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>policy_st_defense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>policy_jj_defense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>policy_wr_defense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴식 중심</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체력과 카디오 집중 훈련</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스탠딩 타격 공격 집중 훈련</x:t>
+    <x:t>policy_jiujitsu_defense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>policy_standing_defense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>policy_jiujitsu_offense</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -942,67 +942,67 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>26</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>36</x:v>
@@ -1017,19 +1017,19 @@
     </x:row>
     <x:row r="5" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>50</x:v>
@@ -1040,19 +1040,19 @@
     </x:row>
     <x:row r="6" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>50</x:v>
@@ -1063,19 +1063,19 @@
     </x:row>
     <x:row r="7" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>50</x:v>
@@ -1086,19 +1086,19 @@
     </x:row>
     <x:row r="8" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>50</x:v>
@@ -1109,19 +1109,19 @@
     </x:row>
     <x:row r="9" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>50</x:v>
@@ -1132,19 +1132,19 @@
     </x:row>
     <x:row r="10" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>50</x:v>
@@ -1155,19 +1155,19 @@
     </x:row>
     <x:row r="11" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>50</x:v>
